--- a/Assets/Lion/Player/Data/Excel/PlayerData.xlsx
+++ b/Assets/Lion/Player/Data/Excel/PlayerData.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vantan\Lion\Assets\Lion\Player\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B7D628-9E6C-4802-A955-6A1AB2004AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5085EC5-A2D9-4371-9ADB-9FED6C3A58BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExpLevelStatusTable" sheetId="1" r:id="rId1"/>
-    <sheet name="ItemLevelUpCostTable" sheetId="2" r:id="rId2"/>
-    <sheet name="ItemLevelStatusTable" sheetId="3" r:id="rId3"/>
+    <sheet name="ExpLevelUpCostTable" sheetId="4" r:id="rId1"/>
+    <sheet name="ExpLevelStatusTable" sheetId="1" r:id="rId2"/>
+    <sheet name="ItemLevelUpCostTable" sheetId="2" r:id="rId3"/>
+    <sheet name="ItemLevelStatusTable" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>Level</t>
     <phoneticPr fontId="1"/>
@@ -396,1706 +397,2325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H121"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD21220-C81E-4049-86A3-399A5C060285}">
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
-        <v>102</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>20</v>
       </c>
-      <c r="C4" s="2">
-        <v>105</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>30</v>
       </c>
-      <c r="C5" s="2">
-        <v>110</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6">
         <v>40</v>
       </c>
-      <c r="C6" s="2">
-        <v>115</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>50</v>
       </c>
-      <c r="C7" s="2">
-        <v>120</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>80</v>
       </c>
-      <c r="C8" s="2">
-        <v>130</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9">
         <v>120</v>
       </c>
-      <c r="C9" s="2">
-        <v>140</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>200</v>
       </c>
-      <c r="C10" s="2">
-        <v>150</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>300</v>
       </c>
-      <c r="C11" s="2">
-        <v>160</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12">
         <v>500</v>
       </c>
-      <c r="C12" s="2">
-        <v>170</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>700</v>
       </c>
-      <c r="C13" s="2">
-        <v>180</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>900</v>
       </c>
-      <c r="C14" s="2">
-        <v>190</v>
-      </c>
-      <c r="D14" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15">
         <v>1200</v>
       </c>
-      <c r="C15" s="2">
-        <v>200</v>
-      </c>
-      <c r="D15" s="2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>1500</v>
       </c>
-      <c r="C16" s="2">
-        <v>220</v>
-      </c>
-      <c r="D16" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>2000</v>
       </c>
-      <c r="C17" s="2">
-        <v>240</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18">
         <v>2500</v>
       </c>
-      <c r="C18" s="2">
-        <v>260</v>
-      </c>
-      <c r="D18" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>3000</v>
       </c>
-      <c r="C19" s="2">
-        <v>280</v>
-      </c>
-      <c r="D19" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>3500</v>
       </c>
-      <c r="C20" s="2">
-        <v>300</v>
-      </c>
-      <c r="D20" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21">
         <v>4000</v>
       </c>
-      <c r="C21" s="2">
-        <v>330</v>
-      </c>
-      <c r="D21" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>4500</v>
       </c>
-      <c r="C22" s="2">
-        <v>360</v>
-      </c>
-      <c r="D22" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>5000</v>
       </c>
-      <c r="C23" s="2">
-        <v>400</v>
-      </c>
-      <c r="D23" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>5500</v>
       </c>
-      <c r="C24" s="2">
-        <v>420</v>
-      </c>
-      <c r="D24" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>6050</v>
       </c>
-      <c r="C25" s="2">
-        <v>440</v>
-      </c>
-      <c r="D25" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>6655</v>
       </c>
-      <c r="C26" s="2">
-        <v>460</v>
-      </c>
-      <c r="D26" s="2">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>7320</v>
       </c>
-      <c r="C27" s="2">
-        <v>480</v>
-      </c>
-      <c r="D27" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>8052</v>
       </c>
-      <c r="C28" s="2">
-        <v>500</v>
-      </c>
-      <c r="D28" s="2">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>8857</v>
       </c>
-      <c r="C29" s="2">
-        <v>520</v>
-      </c>
-      <c r="D29" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>9742</v>
       </c>
-      <c r="C30" s="2">
-        <v>540</v>
-      </c>
-      <c r="D30" s="2">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>10716</v>
       </c>
-      <c r="C31" s="2">
-        <v>560</v>
-      </c>
-      <c r="D31" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>11787</v>
       </c>
-      <c r="C32" s="2">
-        <v>580</v>
-      </c>
-      <c r="D32" s="2">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>12965</v>
       </c>
-      <c r="C33" s="2">
-        <v>600</v>
-      </c>
-      <c r="D33" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>14261</v>
       </c>
-      <c r="C34" s="2">
-        <v>620</v>
-      </c>
-      <c r="D34" s="2">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>15687</v>
       </c>
-      <c r="C35" s="2">
-        <v>640</v>
-      </c>
-      <c r="D35" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>17255</v>
       </c>
-      <c r="C36" s="2">
-        <v>660</v>
-      </c>
-      <c r="D36" s="2">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>18980</v>
       </c>
-      <c r="C37" s="2">
-        <v>680</v>
-      </c>
-      <c r="D37" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>20878</v>
       </c>
-      <c r="C38" s="2">
-        <v>700</v>
-      </c>
-      <c r="D38" s="2">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>22965</v>
       </c>
-      <c r="C39" s="2">
-        <v>720</v>
-      </c>
-      <c r="D39" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>25261</v>
       </c>
-      <c r="C40" s="2">
-        <v>740</v>
-      </c>
-      <c r="D40" s="2">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="2">
         <v>27787</v>
       </c>
-      <c r="C41" s="2">
-        <v>760</v>
-      </c>
-      <c r="D41" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="2">
         <v>30565</v>
       </c>
-      <c r="C42" s="2">
-        <v>780</v>
-      </c>
-      <c r="D42" s="2">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="2">
         <v>33621</v>
       </c>
-      <c r="C43" s="2">
-        <v>800</v>
-      </c>
-      <c r="D43" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="2">
         <v>36983</v>
       </c>
-      <c r="C44" s="2">
-        <v>820</v>
-      </c>
-      <c r="D44" s="2">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="2">
         <v>40681</v>
       </c>
-      <c r="C45" s="2">
-        <v>840</v>
-      </c>
-      <c r="D45" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="2">
         <v>44749</v>
       </c>
-      <c r="C46" s="2">
-        <v>860</v>
-      </c>
-      <c r="D46" s="2">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="2">
         <v>49223</v>
       </c>
-      <c r="C47" s="2">
-        <v>880</v>
-      </c>
-      <c r="D47" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="2">
         <v>54145</v>
       </c>
-      <c r="C48" s="2">
-        <v>900</v>
-      </c>
-      <c r="D48" s="2">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>59559</v>
       </c>
-      <c r="C49" s="2">
-        <v>920</v>
-      </c>
-      <c r="D49" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="2">
         <v>65514</v>
       </c>
-      <c r="C50" s="2">
-        <v>940</v>
-      </c>
-      <c r="D50" s="2">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="2">
         <v>72065</v>
       </c>
-      <c r="C51" s="2">
-        <v>960</v>
-      </c>
-      <c r="D51" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="2">
         <v>79271</v>
       </c>
-      <c r="C52" s="2">
-        <v>980</v>
-      </c>
-      <c r="D52" s="2">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="2">
         <v>87198</v>
       </c>
-      <c r="C53" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D53" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="2">
         <v>95917</v>
       </c>
-      <c r="C54" s="2">
-        <v>1020</v>
-      </c>
-      <c r="D54" s="2">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="2">
         <v>105508</v>
       </c>
-      <c r="C55" s="2">
-        <v>1040</v>
-      </c>
-      <c r="D55" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="2">
         <v>116058</v>
       </c>
-      <c r="C56" s="2">
-        <v>1060</v>
-      </c>
-      <c r="D56" s="2">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" s="2">
         <v>127663</v>
       </c>
-      <c r="C57" s="2">
-        <v>1080</v>
-      </c>
-      <c r="D57" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" s="2">
         <v>140429</v>
       </c>
-      <c r="C58" s="2">
-        <v>1100</v>
-      </c>
-      <c r="D58" s="2">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="2">
         <v>154471</v>
       </c>
-      <c r="C59" s="2">
-        <v>1120</v>
-      </c>
-      <c r="D59" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" s="2">
         <v>169918</v>
       </c>
-      <c r="C60" s="2">
-        <v>1140</v>
-      </c>
-      <c r="D60" s="2">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" s="2">
         <v>186909</v>
       </c>
-      <c r="C61" s="2">
-        <v>1160</v>
-      </c>
-      <c r="D61" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="2">
         <v>205599</v>
       </c>
-      <c r="C62" s="2">
-        <v>1180</v>
-      </c>
-      <c r="D62" s="2">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" s="2">
         <v>226158</v>
       </c>
-      <c r="C63" s="2">
-        <v>1200</v>
-      </c>
-      <c r="D63" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" s="2">
         <v>248773</v>
       </c>
-      <c r="C64" s="2">
-        <v>1220</v>
-      </c>
-      <c r="D64" s="2">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="1">
         <v>64</v>
       </c>
       <c r="B65" s="2">
         <v>273650</v>
       </c>
-      <c r="C65" s="2">
-        <v>1240</v>
-      </c>
-      <c r="D65" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" s="2">
         <v>301015</v>
       </c>
-      <c r="C66" s="2">
-        <v>1260</v>
-      </c>
-      <c r="D66" s="2">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" s="2">
         <v>331116</v>
       </c>
-      <c r="C67" s="2">
-        <v>1280</v>
-      </c>
-      <c r="D67" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" s="2">
         <v>364227</v>
       </c>
-      <c r="C68" s="2">
-        <v>1300</v>
-      </c>
-      <c r="D68" s="2">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="2">
         <v>400649</v>
       </c>
-      <c r="C69" s="2">
-        <v>1320</v>
-      </c>
-      <c r="D69" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" s="2">
         <v>440713</v>
       </c>
-      <c r="C70" s="2">
-        <v>1340</v>
-      </c>
-      <c r="D70" s="2">
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" s="2">
         <v>484784</v>
       </c>
-      <c r="C71" s="2">
-        <v>1360</v>
-      </c>
-      <c r="D71" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="2">
         <v>533262</v>
       </c>
-      <c r="C72" s="2">
-        <v>1380</v>
-      </c>
-      <c r="D72" s="2">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" s="2">
         <v>586588</v>
       </c>
-      <c r="C73" s="2">
-        <v>1400</v>
-      </c>
-      <c r="D73" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" s="2">
         <v>645246</v>
       </c>
-      <c r="C74" s="2">
-        <v>1420</v>
-      </c>
-      <c r="D74" s="2">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="1">
         <v>74</v>
       </c>
       <c r="B75" s="2">
         <v>709770</v>
       </c>
-      <c r="C75" s="2">
-        <v>1440</v>
-      </c>
-      <c r="D75" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" s="2">
         <v>780747</v>
       </c>
-      <c r="C76" s="2">
-        <v>1460</v>
-      </c>
-      <c r="D76" s="2">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" s="2">
         <v>858821</v>
       </c>
-      <c r="C77" s="2">
-        <v>1480</v>
-      </c>
-      <c r="D77" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="1">
         <v>77</v>
       </c>
       <c r="B78" s="2">
         <v>944703</v>
       </c>
-      <c r="C78" s="2">
-        <v>1500</v>
-      </c>
-      <c r="D78" s="2">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" s="2">
         <v>1039173</v>
       </c>
-      <c r="C79" s="2">
-        <v>1520</v>
-      </c>
-      <c r="D79" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" s="2">
         <v>1143090</v>
       </c>
-      <c r="C80" s="2">
-        <v>1540</v>
-      </c>
-      <c r="D80" s="2">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="1">
         <v>80</v>
       </c>
       <c r="B81" s="2">
         <v>1257399</v>
       </c>
-      <c r="C81" s="2">
-        <v>1560</v>
-      </c>
-      <c r="D81" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" s="2">
         <v>1383138</v>
       </c>
-      <c r="C82" s="2">
-        <v>1580</v>
-      </c>
-      <c r="D82" s="2">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="2">
         <v>1521451</v>
       </c>
-      <c r="C83" s="2">
-        <v>1600</v>
-      </c>
-      <c r="D83" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="2">
         <v>1673596</v>
       </c>
-      <c r="C84" s="2">
-        <v>1620</v>
-      </c>
-      <c r="D84" s="2">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" s="2">
         <v>1840955</v>
       </c>
-      <c r="C85" s="2">
-        <v>1640</v>
-      </c>
-      <c r="D85" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="2">
         <v>2025050</v>
       </c>
-      <c r="C86" s="2">
-        <v>1660</v>
-      </c>
-      <c r="D86" s="2">
-        <v>41.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="1">
         <v>86</v>
       </c>
       <c r="B87" s="2">
         <v>2227555</v>
       </c>
-      <c r="C87" s="2">
-        <v>1680</v>
-      </c>
-      <c r="D87" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" s="2">
         <v>2450310</v>
       </c>
-      <c r="C88" s="2">
-        <v>1700</v>
-      </c>
-      <c r="D88" s="2">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" s="2">
         <v>2695341</v>
       </c>
-      <c r="C89" s="2">
-        <v>1720</v>
-      </c>
-      <c r="D89" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" s="2">
         <v>2964875</v>
       </c>
-      <c r="C90" s="2">
-        <v>1740</v>
-      </c>
-      <c r="D90" s="2">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="1">
         <v>90</v>
       </c>
       <c r="B91" s="2">
         <v>3261362</v>
       </c>
-      <c r="C91" s="2">
-        <v>1760</v>
-      </c>
-      <c r="D91" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" s="2">
         <v>3587498</v>
       </c>
-      <c r="C92" s="2">
-        <v>1780</v>
-      </c>
-      <c r="D92" s="2">
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" s="2">
         <v>3946247</v>
       </c>
-      <c r="C93" s="2">
-        <v>1800</v>
-      </c>
-      <c r="D93" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94" s="1">
         <v>93</v>
       </c>
       <c r="B94" s="2">
         <v>4340871</v>
       </c>
-      <c r="C94" s="2">
-        <v>1820</v>
-      </c>
-      <c r="D94" s="2">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" s="2">
         <v>4774958</v>
       </c>
-      <c r="C95" s="2">
-        <v>1840</v>
-      </c>
-      <c r="D95" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" s="2">
         <v>5252453</v>
       </c>
-      <c r="C96" s="2">
-        <v>1860</v>
-      </c>
-      <c r="D96" s="2">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97" s="1">
         <v>96</v>
       </c>
       <c r="B97" s="2">
         <v>5777698</v>
       </c>
-      <c r="C97" s="2">
-        <v>1880</v>
-      </c>
-      <c r="D97" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" s="2">
         <v>6355467</v>
       </c>
-      <c r="C98" s="2">
-        <v>1900</v>
-      </c>
-      <c r="D98" s="2">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" s="2">
         <v>6991013</v>
       </c>
-      <c r="C99" s="2">
-        <v>1920</v>
-      </c>
-      <c r="D99" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100" s="1">
         <v>99</v>
       </c>
       <c r="B100" s="2">
         <v>7690114</v>
       </c>
-      <c r="C100" s="2">
-        <v>1940</v>
-      </c>
-      <c r="D100" s="2">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" s="2">
         <v>8459125</v>
       </c>
-      <c r="C101" s="2">
-        <v>1960</v>
-      </c>
-      <c r="D101" s="2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" s="2">
         <v>9305037</v>
       </c>
-      <c r="C102" s="2">
-        <v>1980</v>
-      </c>
-      <c r="D102" s="2">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103" s="1">
         <v>102</v>
       </c>
       <c r="B103" s="2">
         <v>10235540</v>
       </c>
-      <c r="C103" s="2">
-        <v>2000</v>
-      </c>
-      <c r="D103" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" s="2">
         <v>11259094</v>
       </c>
-      <c r="C104" s="2">
-        <v>2020</v>
-      </c>
-      <c r="D104" s="2">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" s="2">
         <v>12385003</v>
       </c>
-      <c r="C105" s="2">
-        <v>2040</v>
-      </c>
-      <c r="D105" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106" s="1">
         <v>105</v>
       </c>
       <c r="B106" s="2">
         <v>13623503</v>
       </c>
-      <c r="C106" s="2">
-        <v>2060</v>
-      </c>
-      <c r="D106" s="2">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" s="2">
         <v>14985853</v>
       </c>
-      <c r="C107" s="2">
-        <v>2080</v>
-      </c>
-      <c r="D107" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" s="2">
         <v>16484438</v>
       </c>
-      <c r="C108" s="2">
-        <v>2100</v>
-      </c>
-      <c r="D108" s="2">
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109" s="1">
         <v>108</v>
       </c>
       <c r="B109" s="2">
         <v>18132881</v>
       </c>
-      <c r="C109" s="2">
-        <v>2120</v>
-      </c>
-      <c r="D109" s="2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" s="2">
         <v>19946169</v>
       </c>
-      <c r="C110" s="2">
-        <v>2140</v>
-      </c>
-      <c r="D110" s="2">
-        <v>53.5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" s="2">
         <v>21940785</v>
       </c>
-      <c r="C111" s="2">
-        <v>2160</v>
-      </c>
-      <c r="D111" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" s="2">
         <v>24134863</v>
       </c>
-      <c r="C112" s="2">
-        <v>2180</v>
-      </c>
-      <c r="D112" s="2">
-        <v>54.5</v>
-      </c>
-      <c r="H112" s="3"/>
-    </row>
-    <row r="113" spans="1:4">
+    </row>
+    <row r="113" spans="1:2">
       <c r="A113" s="1">
         <v>112</v>
       </c>
       <c r="B113" s="2">
         <v>26548349</v>
       </c>
-      <c r="C113" s="2">
-        <v>2200</v>
-      </c>
-      <c r="D113" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
+    </row>
+    <row r="114" spans="1:2">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" s="2">
         <v>29203183</v>
       </c>
-      <c r="C114" s="2">
-        <v>2220</v>
-      </c>
-      <c r="D114" s="2">
-        <v>55.5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
+    </row>
+    <row r="115" spans="1:2">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" s="2">
         <v>32123501</v>
       </c>
-      <c r="C115" s="2">
-        <v>2240</v>
-      </c>
-      <c r="D115" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116" s="1">
         <v>115</v>
       </c>
       <c r="B116" s="2">
         <v>35335851</v>
       </c>
-      <c r="C116" s="2">
-        <v>2260</v>
-      </c>
-      <c r="D116" s="2">
-        <v>56.5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" s="2">
         <v>38869436</v>
       </c>
-      <c r="C117" s="2">
-        <v>2280</v>
-      </c>
-      <c r="D117" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
+    </row>
+    <row r="118" spans="1:2">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" s="2">
         <v>42756379</v>
       </c>
-      <c r="C118" s="2">
-        <v>2300</v>
-      </c>
-      <c r="D118" s="2">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+    </row>
+    <row r="119" spans="1:2">
       <c r="A119" s="1">
         <v>118</v>
       </c>
       <c r="B119" s="2">
         <v>47032016</v>
       </c>
-      <c r="C119" s="2">
-        <v>2320</v>
-      </c>
-      <c r="D119" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
+    </row>
+    <row r="120" spans="1:2">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" s="2">
         <v>51735217</v>
       </c>
-      <c r="C120" s="2">
-        <v>2340</v>
-      </c>
-      <c r="D120" s="2">
-        <v>58.5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+    </row>
+    <row r="121" spans="1:2">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" s="2">
         <v>56908738</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G121"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="3" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>102</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>105</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>110</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>115</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>120</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>130</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>140</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>150</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>160</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>170</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>180</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>190</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>200</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>220</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>240</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>260</v>
+      </c>
+      <c r="C18" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>280</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>300</v>
+      </c>
+      <c r="C20" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>330</v>
+      </c>
+      <c r="C21" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>360</v>
+      </c>
+      <c r="C22" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>400</v>
+      </c>
+      <c r="C23" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>420</v>
+      </c>
+      <c r="C24" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>440</v>
+      </c>
+      <c r="C25" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>460</v>
+      </c>
+      <c r="C26" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>480</v>
+      </c>
+      <c r="C27" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>500</v>
+      </c>
+      <c r="C28" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>520</v>
+      </c>
+      <c r="C29" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>540</v>
+      </c>
+      <c r="C30" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>560</v>
+      </c>
+      <c r="C31" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>580</v>
+      </c>
+      <c r="C32" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>600</v>
+      </c>
+      <c r="C33" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>620</v>
+      </c>
+      <c r="C34" s="2">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>640</v>
+      </c>
+      <c r="C35" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>660</v>
+      </c>
+      <c r="C36" s="2">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>680</v>
+      </c>
+      <c r="C37" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>700</v>
+      </c>
+      <c r="C38" s="2">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>720</v>
+      </c>
+      <c r="C39" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>740</v>
+      </c>
+      <c r="C40" s="2">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>760</v>
+      </c>
+      <c r="C41" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>780</v>
+      </c>
+      <c r="C42" s="2">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>800</v>
+      </c>
+      <c r="C43" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>820</v>
+      </c>
+      <c r="C44" s="2">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>840</v>
+      </c>
+      <c r="C45" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>860</v>
+      </c>
+      <c r="C46" s="2">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>880</v>
+      </c>
+      <c r="C47" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>900</v>
+      </c>
+      <c r="C48" s="2">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>920</v>
+      </c>
+      <c r="C49" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>940</v>
+      </c>
+      <c r="C50" s="2">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>960</v>
+      </c>
+      <c r="C51" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>980</v>
+      </c>
+      <c r="C52" s="2">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C53" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1020</v>
+      </c>
+      <c r="C54" s="2">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1040</v>
+      </c>
+      <c r="C55" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1060</v>
+      </c>
+      <c r="C56" s="2">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>1080</v>
+      </c>
+      <c r="C57" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>1100</v>
+      </c>
+      <c r="C58" s="2">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1120</v>
+      </c>
+      <c r="C59" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>1140</v>
+      </c>
+      <c r="C60" s="2">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>1160</v>
+      </c>
+      <c r="C61" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>1180</v>
+      </c>
+      <c r="C62" s="2">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C63" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>1220</v>
+      </c>
+      <c r="C64" s="2">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>1240</v>
+      </c>
+      <c r="C65" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>1260</v>
+      </c>
+      <c r="C66" s="2">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>1280</v>
+      </c>
+      <c r="C67" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>1300</v>
+      </c>
+      <c r="C68" s="2">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>1320</v>
+      </c>
+      <c r="C69" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>1340</v>
+      </c>
+      <c r="C70" s="2">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>1360</v>
+      </c>
+      <c r="C71" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>1380</v>
+      </c>
+      <c r="C72" s="2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>1400</v>
+      </c>
+      <c r="C73" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>1420</v>
+      </c>
+      <c r="C74" s="2">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2">
+        <v>1440</v>
+      </c>
+      <c r="C75" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>1460</v>
+      </c>
+      <c r="C76" s="2">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C77" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C78" s="2">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>1520</v>
+      </c>
+      <c r="C79" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>1540</v>
+      </c>
+      <c r="C80" s="2">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>1560</v>
+      </c>
+      <c r="C81" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>1580</v>
+      </c>
+      <c r="C82" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>1600</v>
+      </c>
+      <c r="C83" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
+        <v>1620</v>
+      </c>
+      <c r="C84" s="2">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>1640</v>
+      </c>
+      <c r="C85" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>1660</v>
+      </c>
+      <c r="C86" s="2">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>1680</v>
+      </c>
+      <c r="C87" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>1700</v>
+      </c>
+      <c r="C88" s="2">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2">
+        <v>1720</v>
+      </c>
+      <c r="C89" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2">
+        <v>1740</v>
+      </c>
+      <c r="C90" s="2">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2">
+        <v>1760</v>
+      </c>
+      <c r="C91" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2">
+        <v>1780</v>
+      </c>
+      <c r="C92" s="2">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2">
+        <v>1800</v>
+      </c>
+      <c r="C93" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2">
+        <v>1820</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2">
+        <v>1840</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C96" s="2">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2">
+        <v>1880</v>
+      </c>
+      <c r="C97" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2">
+        <v>1900</v>
+      </c>
+      <c r="C98" s="2">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2">
+        <v>1920</v>
+      </c>
+      <c r="C99" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2">
+        <v>1940</v>
+      </c>
+      <c r="C100" s="2">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2">
+        <v>1960</v>
+      </c>
+      <c r="C101" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2">
+        <v>1980</v>
+      </c>
+      <c r="C102" s="2">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C103" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2">
+        <v>2020</v>
+      </c>
+      <c r="C104" s="2">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2">
+        <v>2040</v>
+      </c>
+      <c r="C105" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2">
+        <v>2060</v>
+      </c>
+      <c r="C106" s="2">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2">
+        <v>2080</v>
+      </c>
+      <c r="C107" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2">
+        <v>2100</v>
+      </c>
+      <c r="C108" s="2">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2">
+        <v>2120</v>
+      </c>
+      <c r="C109" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2">
+        <v>2140</v>
+      </c>
+      <c r="C110" s="2">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2">
+        <v>2160</v>
+      </c>
+      <c r="C111" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2">
+        <v>2180</v>
+      </c>
+      <c r="C112" s="2">
+        <v>54.5</v>
+      </c>
+      <c r="G112" s="3"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2">
+        <v>2200</v>
+      </c>
+      <c r="C113" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2">
+        <v>2220</v>
+      </c>
+      <c r="C114" s="2">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2">
+        <v>2240</v>
+      </c>
+      <c r="C115" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2">
+        <v>2260</v>
+      </c>
+      <c r="C116" s="2">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2">
+        <v>2280</v>
+      </c>
+      <c r="C117" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2">
+        <v>2300</v>
+      </c>
+      <c r="C118" s="2">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2">
+        <v>2320</v>
+      </c>
+      <c r="C119" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2">
+        <v>2340</v>
+      </c>
+      <c r="C120" s="2">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2">
+        <v>2360</v>
+      </c>
       <c r="C121" s="2">
-        <v>2360</v>
-      </c>
-      <c r="D121" s="2">
         <v>59</v>
       </c>
     </row>
@@ -2105,7 +2725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5699D5E0-3B32-42EC-8611-C34466845F4A}">
   <dimension ref="A1:C119"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2844,7 +3464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBDF95B-BB9F-4638-9058-846CC92DE057}">
   <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
